--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.15882762647938</v>
+        <v>3.438309489302899</v>
       </c>
       <c r="D2" t="n">
-        <v>21.1326476923228</v>
+        <v>3.434055250002454</v>
       </c>
       <c r="E2" t="n">
-        <v>7.557331398286328</v>
+        <v>1.228066352221528</v>
       </c>
       <c r="F2" t="n">
-        <v>7.554950627067018</v>
+        <v>1.22767947689839</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.21773664571858</v>
+        <v>4.26038220492927</v>
       </c>
       <c r="D3" t="n">
-        <v>26.21773664571858</v>
+        <v>4.26038220492927</v>
       </c>
       <c r="E3" t="n">
-        <v>7.557331398286328</v>
+        <v>1.228066352221528</v>
       </c>
       <c r="F3" t="n">
-        <v>7.554950627067018</v>
+        <v>1.22767947689839</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.267022782947729</v>
+        <v>1.343391202229006</v>
       </c>
       <c r="D4" t="n">
-        <v>8.265644539371381</v>
+        <v>1.34316723764785</v>
       </c>
       <c r="E4" t="n">
-        <v>7.557331398286328</v>
+        <v>1.228066352221528</v>
       </c>
       <c r="F4" t="n">
-        <v>7.554950627067018</v>
+        <v>1.22767947689839</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
